--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z936"/>
+  <dimension ref="A1:Z937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53002,14 +53002,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 1916-2024</t>
+          <t>A 2040-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -53059,14 +53059,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 1950-2024</t>
+          <t>A 1916-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -53116,14 +53116,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 1917-2024</t>
+          <t>A 1949-2024</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53173,14 +53173,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 1949-2024</t>
+          <t>A 1917-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53230,14 +53230,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 2040-2024</t>
+          <t>A 1950-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53401,14 +53401,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 2836-2024</t>
+          <t>A 2843-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53458,14 +53458,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 2843-2024</t>
+          <t>A 2940-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53515,14 +53515,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 2940-2024</t>
+          <t>A 2836-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53743,14 +53743,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 4128-2024</t>
+          <t>A 4135-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53800,14 +53800,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 4135-2024</t>
+          <t>A 4128-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54028,14 +54028,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54370,14 +54370,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54427,14 +54427,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 4855-2024</t>
+          <t>A 4926-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54484,14 +54484,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 4926-2024</t>
+          <t>A 4855-2024</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54541,14 +54541,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5305-2024</t>
+          <t>A 5298-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5298-2024</t>
+          <t>A 5305-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,8 +54684,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G932" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54722,14 +54727,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54741,13 +54746,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G933" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54848,7 +54848,7 @@
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
       </c>
       <c r="R935" s="2" t="inlineStr"/>
     </row>
-    <row r="936">
+    <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
           <t>A 5761-2024</t>
@@ -54905,7 +54905,7 @@
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54951,6 +54951,68 @@
         <v>0</v>
       </c>
       <c r="R936" s="2" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>A 6129-2024</t>
+        </is>
+      </c>
+      <c r="B937" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C937" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G937" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H937" t="n">
+        <v>0</v>
+      </c>
+      <c r="I937" t="n">
+        <v>0</v>
+      </c>
+      <c r="J937" t="n">
+        <v>0</v>
+      </c>
+      <c r="K937" t="n">
+        <v>0</v>
+      </c>
+      <c r="L937" t="n">
+        <v>0</v>
+      </c>
+      <c r="M937" t="n">
+        <v>0</v>
+      </c>
+      <c r="N937" t="n">
+        <v>0</v>
+      </c>
+      <c r="O937" t="n">
+        <v>0</v>
+      </c>
+      <c r="P937" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q937" t="n">
+        <v>0</v>
+      </c>
+      <c r="R937" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53743,14 +53743,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 4135-2024</t>
+          <t>A 4128-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53800,14 +53800,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 4128-2024</t>
+          <t>A 4135-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54035,7 +54035,7 @@
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54377,7 +54377,7 @@
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54541,14 +54541,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5298-2024</t>
+          <t>A 5305-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5305-2024</t>
+          <t>A 5298-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54672,7 +54672,7 @@
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z937"/>
+  <dimension ref="A1:Z938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53458,14 +53458,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 2940-2024</t>
+          <t>A 2836-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53515,14 +53515,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 2836-2024</t>
+          <t>A 2940-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54028,14 +54028,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54206,7 +54206,7 @@
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54427,14 +54427,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 4926-2024</t>
+          <t>A 4855-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54484,14 +54484,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 4855-2024</t>
+          <t>A 4926-2024</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54548,7 +54548,7 @@
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,13 +54684,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F932" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G932" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54727,14 +54722,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54746,8 +54741,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G933" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54848,7 +54848,7 @@
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
       </c>
       <c r="R936" s="2" t="inlineStr"/>
     </row>
-    <row r="937">
+    <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
           <t>A 6129-2024</t>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55013,6 +55013,63 @@
         <v>0</v>
       </c>
       <c r="R937" s="2" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>A 6631-2024</t>
+        </is>
+      </c>
+      <c r="B938" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C938" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G938" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H938" t="n">
+        <v>0</v>
+      </c>
+      <c r="I938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J938" t="n">
+        <v>0</v>
+      </c>
+      <c r="K938" t="n">
+        <v>0</v>
+      </c>
+      <c r="L938" t="n">
+        <v>0</v>
+      </c>
+      <c r="M938" t="n">
+        <v>0</v>
+      </c>
+      <c r="N938" t="n">
+        <v>0</v>
+      </c>
+      <c r="O938" t="n">
+        <v>0</v>
+      </c>
+      <c r="P938" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q938" t="n">
+        <v>0</v>
+      </c>
+      <c r="R938" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z938"/>
+  <dimension ref="A1:Z943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53401,14 +53401,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 2843-2024</t>
+          <t>A 2940-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53458,14 +53458,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 2836-2024</t>
+          <t>A 2843-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53515,14 +53515,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 2940-2024</t>
+          <t>A 2836-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53743,14 +53743,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 4128-2024</t>
+          <t>A 4135-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53800,14 +53800,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 4135-2024</t>
+          <t>A 4128-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54028,14 +54028,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54370,14 +54370,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,8 +54684,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G932" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54722,14 +54727,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54741,13 +54746,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G933" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54848,7 +54848,7 @@
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
       </c>
       <c r="R937" s="2" t="inlineStr"/>
     </row>
-    <row r="938">
+    <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
           <t>A 6631-2024</t>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55070,6 +55070,291 @@
         <v>0</v>
       </c>
       <c r="R938" s="2" t="inlineStr"/>
+    </row>
+    <row r="939" ht="15" customHeight="1">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>A 6912-2024</t>
+        </is>
+      </c>
+      <c r="B939" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C939" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G939" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H939" t="n">
+        <v>0</v>
+      </c>
+      <c r="I939" t="n">
+        <v>0</v>
+      </c>
+      <c r="J939" t="n">
+        <v>0</v>
+      </c>
+      <c r="K939" t="n">
+        <v>0</v>
+      </c>
+      <c r="L939" t="n">
+        <v>0</v>
+      </c>
+      <c r="M939" t="n">
+        <v>0</v>
+      </c>
+      <c r="N939" t="n">
+        <v>0</v>
+      </c>
+      <c r="O939" t="n">
+        <v>0</v>
+      </c>
+      <c r="P939" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q939" t="n">
+        <v>0</v>
+      </c>
+      <c r="R939" s="2" t="inlineStr"/>
+    </row>
+    <row r="940" ht="15" customHeight="1">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>A 6915-2024</t>
+        </is>
+      </c>
+      <c r="B940" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C940" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G940" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H940" t="n">
+        <v>0</v>
+      </c>
+      <c r="I940" t="n">
+        <v>0</v>
+      </c>
+      <c r="J940" t="n">
+        <v>0</v>
+      </c>
+      <c r="K940" t="n">
+        <v>0</v>
+      </c>
+      <c r="L940" t="n">
+        <v>0</v>
+      </c>
+      <c r="M940" t="n">
+        <v>0</v>
+      </c>
+      <c r="N940" t="n">
+        <v>0</v>
+      </c>
+      <c r="O940" t="n">
+        <v>0</v>
+      </c>
+      <c r="P940" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q940" t="n">
+        <v>0</v>
+      </c>
+      <c r="R940" s="2" t="inlineStr"/>
+    </row>
+    <row r="941" ht="15" customHeight="1">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>A 6914-2024</t>
+        </is>
+      </c>
+      <c r="B941" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C941" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G941" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H941" t="n">
+        <v>0</v>
+      </c>
+      <c r="I941" t="n">
+        <v>0</v>
+      </c>
+      <c r="J941" t="n">
+        <v>0</v>
+      </c>
+      <c r="K941" t="n">
+        <v>0</v>
+      </c>
+      <c r="L941" t="n">
+        <v>0</v>
+      </c>
+      <c r="M941" t="n">
+        <v>0</v>
+      </c>
+      <c r="N941" t="n">
+        <v>0</v>
+      </c>
+      <c r="O941" t="n">
+        <v>0</v>
+      </c>
+      <c r="P941" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q941" t="n">
+        <v>0</v>
+      </c>
+      <c r="R941" s="2" t="inlineStr"/>
+    </row>
+    <row r="942" ht="15" customHeight="1">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>A 6918-2024</t>
+        </is>
+      </c>
+      <c r="B942" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C942" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G942" t="n">
+        <v>5</v>
+      </c>
+      <c r="H942" t="n">
+        <v>0</v>
+      </c>
+      <c r="I942" t="n">
+        <v>0</v>
+      </c>
+      <c r="J942" t="n">
+        <v>0</v>
+      </c>
+      <c r="K942" t="n">
+        <v>0</v>
+      </c>
+      <c r="L942" t="n">
+        <v>0</v>
+      </c>
+      <c r="M942" t="n">
+        <v>0</v>
+      </c>
+      <c r="N942" t="n">
+        <v>0</v>
+      </c>
+      <c r="O942" t="n">
+        <v>0</v>
+      </c>
+      <c r="P942" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q942" t="n">
+        <v>0</v>
+      </c>
+      <c r="R942" s="2" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>A 7017-2024</t>
+        </is>
+      </c>
+      <c r="B943" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C943" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G943" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H943" t="n">
+        <v>0</v>
+      </c>
+      <c r="I943" t="n">
+        <v>0</v>
+      </c>
+      <c r="J943" t="n">
+        <v>0</v>
+      </c>
+      <c r="K943" t="n">
+        <v>0</v>
+      </c>
+      <c r="L943" t="n">
+        <v>0</v>
+      </c>
+      <c r="M943" t="n">
+        <v>0</v>
+      </c>
+      <c r="N943" t="n">
+        <v>0</v>
+      </c>
+      <c r="O943" t="n">
+        <v>0</v>
+      </c>
+      <c r="P943" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q943" t="n">
+        <v>0</v>
+      </c>
+      <c r="R943" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z943"/>
+  <dimension ref="A1:Z945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53401,14 +53401,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 2940-2024</t>
+          <t>A 2843-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53458,14 +53458,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 2843-2024</t>
+          <t>A 2940-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53743,14 +53743,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 4135-2024</t>
+          <t>A 4128-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53800,14 +53800,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 4128-2024</t>
+          <t>A 4135-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54035,7 +54035,7 @@
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54370,14 +54370,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,13 +54684,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F932" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G932" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54727,14 +54722,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54746,8 +54741,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G933" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54848,7 +54848,7 @@
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
       </c>
       <c r="R942" s="2" t="inlineStr"/>
     </row>
-    <row r="943">
+    <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
           <t>A 7017-2024</t>
@@ -55309,7 +55309,7 @@
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55355,6 +55355,120 @@
         <v>0</v>
       </c>
       <c r="R943" s="2" t="inlineStr"/>
+    </row>
+    <row r="944" ht="15" customHeight="1">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>A 7202-2024</t>
+        </is>
+      </c>
+      <c r="B944" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C944" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G944" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I944" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" t="n">
+        <v>0</v>
+      </c>
+      <c r="K944" t="n">
+        <v>0</v>
+      </c>
+      <c r="L944" t="n">
+        <v>0</v>
+      </c>
+      <c r="M944" t="n">
+        <v>0</v>
+      </c>
+      <c r="N944" t="n">
+        <v>0</v>
+      </c>
+      <c r="O944" t="n">
+        <v>0</v>
+      </c>
+      <c r="P944" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q944" t="n">
+        <v>0</v>
+      </c>
+      <c r="R944" s="2" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>A 7241-2024</t>
+        </is>
+      </c>
+      <c r="B945" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C945" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>VÄRNAMO</t>
+        </is>
+      </c>
+      <c r="G945" t="n">
+        <v>1</v>
+      </c>
+      <c r="H945" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0</v>
+      </c>
+      <c r="J945" t="n">
+        <v>0</v>
+      </c>
+      <c r="K945" t="n">
+        <v>0</v>
+      </c>
+      <c r="L945" t="n">
+        <v>0</v>
+      </c>
+      <c r="M945" t="n">
+        <v>0</v>
+      </c>
+      <c r="N945" t="n">
+        <v>0</v>
+      </c>
+      <c r="O945" t="n">
+        <v>0</v>
+      </c>
+      <c r="P945" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q945" t="n">
+        <v>0</v>
+      </c>
+      <c r="R945" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54370,14 +54370,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54541,14 +54541,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5305-2024</t>
+          <t>A 5298-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5298-2024</t>
+          <t>A 5305-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54729,7 +54729,7 @@
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55074,14 +55074,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 6912-2024</t>
+          <t>A 6915-2024</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -55131,14 +55131,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 6915-2024</t>
+          <t>A 6912-2024</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55195,7 +55195,7 @@
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45344</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45344</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54028,14 +54028,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4788-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4792-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54199,14 +54199,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4788-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54256,14 +54256,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4792-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54320,7 +54320,7 @@
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54427,14 +54427,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 4855-2024</t>
+          <t>A 4926-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54484,14 +54484,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 4926-2024</t>
+          <t>A 4855-2024</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54541,14 +54541,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5298-2024</t>
+          <t>A 5305-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5305-2024</t>
+          <t>A 5298-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,8 +54684,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G932" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54722,14 +54727,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54741,13 +54746,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G933" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55131,14 +55131,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 6912-2024</t>
+          <t>A 6914-2024</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55188,14 +55188,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 6914-2024</t>
+          <t>A 6918-2024</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55245,14 +55245,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 6918-2024</t>
+          <t>A 7017-2024</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55302,14 +55302,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 7017-2024</t>
+          <t>A 6912-2024</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55366,7 +55366,7 @@
         <v>45344</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45344</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54035,7 +54035,7 @@
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54206,7 +54206,7 @@
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,13 +54684,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F932" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G932" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54727,14 +54722,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54746,8 +54741,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G933" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55074,14 +55074,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 6915-2024</t>
+          <t>A 6912-2024</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -55138,7 +55138,7 @@
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55302,14 +55302,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 6912-2024</t>
+          <t>A 6915-2024</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55366,7 +55366,7 @@
         <v>45344</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45344</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53743,14 +53743,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 4128-2024</t>
+          <t>A 4135-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53800,14 +53800,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 4135-2024</t>
+          <t>A 4128-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54028,14 +54028,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4760-2024</t>
+          <t>A 4735-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -54085,14 +54085,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4793-2024</t>
+          <t>A 4787-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -54142,14 +54142,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4735-2024</t>
+          <t>A 4791-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54206,7 +54206,7 @@
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54313,14 +54313,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 4787-2024</t>
+          <t>A 4760-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54370,14 +54370,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 4791-2024</t>
+          <t>A 4793-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54427,14 +54427,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 4926-2024</t>
+          <t>A 4855-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54484,14 +54484,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 4855-2024</t>
+          <t>A 4926-2024</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54548,7 +54548,7 @@
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54665,14 +54665,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5490-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54684,8 +54684,13 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G932" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54722,14 +54727,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5490-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54741,13 +54746,8 @@
           <t>VÄRNAMO</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G933" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55131,14 +55131,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 6914-2024</t>
+          <t>A 6915-2024</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55188,14 +55188,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 6918-2024</t>
+          <t>A 7017-2024</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55245,14 +55245,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 7017-2024</t>
+          <t>A 6914-2024</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55302,14 +55302,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 6915-2024</t>
+          <t>A 6918-2024</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55366,7 +55366,7 @@
         <v>45344</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45344</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44853</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44853</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44854</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44854</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44858</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44858</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44859</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44869</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44869</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44869</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>44869</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44879</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44881</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44882</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>44882</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44886</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>44887</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44887</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44888</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44890</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44897</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44903</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44909</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44915</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44928</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44928</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44929</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44931</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44931</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44936</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44936</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44949</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44949</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>44950</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>44956</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44956</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44957</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44957</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44957</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44966</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44966</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44970</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44970</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44971</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44973</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44973</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44981</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44984</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44984</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44985</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44985</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44992</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44993</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44993</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44994</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44998</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44998</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44998</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45002</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45002</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45007</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45009</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45009</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45009</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45012</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45012</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45020</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45021</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45022</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45029</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45029</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45036</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45036</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45043</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45044</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45044</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45044</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45055</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45056</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45056</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45056</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45056</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45069</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45069</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45072</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45072</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45072</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45072</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45076</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45076</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45078</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45090</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45091</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45091</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45092</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45093</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45093</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45093</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45093</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45093</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45098</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45099</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45102</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45104</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45105</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45106</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45106</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45112</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45112</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45113</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45113</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45114</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45116</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45120</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45124</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45137</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45146</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45146</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45149</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45152</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45154</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45154</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45154</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45155</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45155</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45155</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45155</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45160</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45160</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45160</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45160</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45161</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45162</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45162</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45162</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45162</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45162</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45166</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45166</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45167</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45167</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45167</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45167</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45167</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45170</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45170</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45173</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45173</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45174</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45174</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45175</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45175</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45176</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45176</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45176</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45180</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45180</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45182</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45182</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45183</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45184</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45184</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45184</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45187</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45188</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45188</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45188</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45188</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45189</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45190</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45191</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45191</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45191</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45191</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45191</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45194</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45194</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45196</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45196</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45197</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45197</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45197</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45198</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45198</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45198</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45200</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45200</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45200</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45200</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45204</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45205</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45208</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45208</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45216</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45217</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45217</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45219</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45221</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45221</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45221</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45223</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45223</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45223</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45223</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45223</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45224</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45229</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45231</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45237</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45237</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45237</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45238</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45238</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45238</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45238</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45238</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45238</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45238</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45238</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45239</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45239</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45240</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45240</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45240</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45240</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45241</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45243</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45243</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45243</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45243</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45243</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45243</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45244</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45245</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45245</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45245</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45250</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45250</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45250</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45250</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45251</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45252</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45254</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45254</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45254</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45257</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45258</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45260</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45260</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45261</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45265</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45267</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45267</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45267</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45267</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45267</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45267</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45270</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45271</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45271</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45271</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45271</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45271</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45272</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45272</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45272</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45273</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45274</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45274</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45275</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45278</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45278</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45278</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45278</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>45279</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45279</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45299</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45302</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45302</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45302</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45302</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45303</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45303</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45306</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45306</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45307</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45307</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45308</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45308</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45308</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45308</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45308</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45309</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45313</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45315</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45315</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45315</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45320</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45321</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45322</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45323</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45323</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53914,14 +53914,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 4438-2024</t>
+          <t>A 4441-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53971,14 +53971,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 4441-2024</t>
+          <t>A 4438-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.7</v>
+        <v>12.6</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54035,7 +54035,7 @@
         <v>45328</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45328</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>45328</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45328</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>45328</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>45328</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>45328</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45329</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45329</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54541,14 +54541,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5305-2024</t>
+          <t>A 5298-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5298-2024</t>
+          <t>A 5305-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54672,7 +54672,7 @@
         <v>45334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54727,14 +54727,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 5681-2024</t>
+          <t>A 5675-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54784,14 +54784,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 5675-2024</t>
+          <t>A 5681-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54841,14 +54841,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 5761-2024</t>
+          <t>A 5763-2024</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54898,14 +54898,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 5763-2024</t>
+          <t>A 5761-2024</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54962,7 +54962,7 @@
         <v>45337</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45341</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55074,14 +55074,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 6912-2024</t>
+          <t>A 6915-2024</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -55131,14 +55131,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 6915-2024</t>
+          <t>A 6912-2024</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55195,7 +55195,7 @@
         <v>45343</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45343</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45343</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55359,14 +55359,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 7202-2024</t>
+          <t>A 7241-2024</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55416,14 +55416,14 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 7241-2024</t>
+          <t>A 7202-2024</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -569,7 +569,7 @@
         <v>44252</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>44420</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>43844</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45077</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>43346</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44546</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>44841</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45008</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>43570</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>43873</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44508</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44602</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44879</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44895</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44979</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45091</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>43320</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>43325</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>43341</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>43346</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>43346</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>43347</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>43353</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>43354</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43356</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>43357</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>43362</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>43364</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>43368</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>43368</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>43372</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>43381</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>43382</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>43384</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>43392</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43392</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>43395</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>43395</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>43396</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>43398</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>43398</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>43399</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>43403</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>43405</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>43409</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43410</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43410</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43410</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>43415</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>43418</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>43418</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>43418</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>43419</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>43419</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>43419</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>43420</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>43423</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>43424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>43424</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43427</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>43431</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>43431</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>43433</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>43437</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>43437</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>43438</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>43438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43438</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43439</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43446</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43448</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43454</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43455</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43455</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43455</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43463</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>43472</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>43473</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>43474</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>43475</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43479</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>43479</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>43479</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>43486</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>43486</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>43486</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>43486</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>43486</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>43489</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>43490</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>43494</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>43504</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>43509</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>43514</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>43514</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>43515</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43516</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>43518</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>43518</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>43529</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43530</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>43542</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>43542</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>43542</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>43545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>43545</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>43549</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>43551</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>43556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>43557</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>43557</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>43557</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>43563</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>43573</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>43584</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43584</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43601</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43601</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>43606</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>43608</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>43616</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>43619</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43627</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43627</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43627</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43630</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43636</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>43639</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>43640</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>43641</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>43641</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>43649</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>43649</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43682</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43682</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43686</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43689</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>43689</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>43690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>43690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43697</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>43703</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>43706</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>43717</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>43719</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>43720</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>43721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>43724</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>43725</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>43725</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>43740</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>43742</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>43744</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>43744</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>43748</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43755</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43766</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43767</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43767</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43767</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43769</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43769</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>43772</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43773</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43783</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43783</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43783</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43784</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43790</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43796</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43802</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43803</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43815</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43826</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43838</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43839</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43844</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43847</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43859</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43866</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43866</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43867</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43871</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43873</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43878</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43881</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43881</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43881</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43886</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43888</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>43888</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>43888</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>43888</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>43888</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43888</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>43889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>43889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>43895</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>43895</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>43895</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>43896</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>43903</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>43907</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>43913</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>43914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>43916</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>43916</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>43916</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>43928</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>43941</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>43943</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>43950</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>43956</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>43962</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>43963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>43974</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>43978</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>43987</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>43987</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>43993</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>43996</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>43997</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>43997</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44004</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44006</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44006</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44022</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44022</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44022</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44029</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44031</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44040</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44048</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44049</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44067</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44068</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44071</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44071</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44078</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44080</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44081</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44092</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44111</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44126</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44139</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44139</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44145</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44147</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44147</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44147</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44151</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44153</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44153</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44165</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44168</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44169</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44169</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44171</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44172</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44176</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44178</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>44178</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44178</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44178</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44181</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44201</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44203</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44204</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44204</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44204</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44209</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44210</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44211</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44214</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44214</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44214</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44216</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44216</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44218</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44218</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44218</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44218</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44218</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44223</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44224</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44229</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44235</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44235</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44246</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44246</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44249</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44258</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44263</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44267</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44270</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44277</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44278</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44278</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44278</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44278</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44284</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44286</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44295</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44295</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44313</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44315</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44315</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44320</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44320</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44322</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44322</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44327</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44341</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44341</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44341</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44348</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44351</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44356</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44361</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44361</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44361</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44361</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44363</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44365</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44377</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44381</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44385</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44392</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44419</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44420</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44425</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44425</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44427</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44434</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44436</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44438</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44438</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44440</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44440</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44441</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44442</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44446</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44448</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44449</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44449</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44449</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44459</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44460</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44462</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44468</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44470</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44470</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44470</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44473</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44473</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44477</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44480</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44489</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44494</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44494</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44496</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>44496</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>44496</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44501</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44515</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44523</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44525</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44526</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44526</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44526</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44532</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44532</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44532</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>44532</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44539</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44539</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44543</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44552</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44552</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44553</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44553</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44557</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44558</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44559</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44559</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44559</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44566</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44566</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44566</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44566</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44566</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44572</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44577</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44595</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44599</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44599</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44599</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44600</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44602</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44602</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44602</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44606</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44607</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44608</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44608</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44616</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44616</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44617</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44628</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44629</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44629</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>44638</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44641</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44642</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44642</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44642</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>44644</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>44644</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44644</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44644</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44644</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>44648</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44649</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44652</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44653</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44653</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44662</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44677</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44678</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44678</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44678</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44686</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44693</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44698</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44699</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44701</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44706</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44721</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44722</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44722</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44727</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44729</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44734</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44753</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44757</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44760</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44770</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44776</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44776</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44776</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44788</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44788</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44788</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44797</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44804</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44805</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44820</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44823</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44823</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44825</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44831</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44837</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44840</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44840</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44840</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44840</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44841</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44844</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44846</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44846</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44846</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44846</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44848</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44851</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44851</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44853</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44853</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44853</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v